--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_4/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8704,0.0473,0.0106,0.0164</t>
-  </si>
-  <si>
-    <t>0.8298,0.0304,0.0181,0.0813</t>
-  </si>
-  <si>
-    <t>0.7968,0.0274,0.0048,0.0493</t>
-  </si>
-  <si>
-    <t>0.8606,0.0170,0.0057,0.0535</t>
-  </si>
-  <si>
-    <t>0.8633,0.0434,0.0037,0.0129</t>
-  </si>
-  <si>
-    <t>0.8338,0.0296,0.0039,0.0324</t>
-  </si>
-  <si>
-    <t>0.9249,0.0235,0.0031,0.0096</t>
-  </si>
-  <si>
-    <t>0.7861,0.0904,0.0126,0.0243</t>
-  </si>
-  <si>
-    <t>0.7252,0.0401,0.0079,0.0756</t>
-  </si>
-  <si>
-    <t>0.7752,0.0906,0.0162,0.0297</t>
-  </si>
-  <si>
-    <t>0.8127,0.0921,0.0131,0.0216</t>
-  </si>
-  <si>
-    <t>0.9313,0.0181,0.0019,0.0085</t>
-  </si>
-  <si>
-    <t>0.8871,0.0158,0.0299,0.0395</t>
-  </si>
-  <si>
-    <t>0.6620,0.1558,0.1496,0.0535</t>
-  </si>
-  <si>
-    <t>0.8186,0.0250,0.1384,0.0218</t>
-  </si>
-  <si>
-    <t>0.5789,0.0974,0.3388,0.0438</t>
-  </si>
-  <si>
-    <t>0.8011,0.0501,0.0745,0.0496</t>
-  </si>
-  <si>
-    <t>0.1682,0.7881,0.0149,0.0083</t>
-  </si>
-  <si>
-    <t>0.2307,0.7451,0.0226,0.0076</t>
-  </si>
-  <si>
-    <t>0.7484,0.0813,0.0076,0.0240</t>
-  </si>
-  <si>
-    <t>0.5309,0.2609,0.0163,0.0217</t>
-  </si>
-  <si>
-    <t>0.2343,0.7887,0.0439,0.0071</t>
-  </si>
-  <si>
-    <t>0.8909,0.0203,0.0419,0.0273</t>
-  </si>
-  <si>
-    <t>0.9496,0.0078,0.0131,0.0150</t>
-  </si>
-  <si>
-    <t>0.7124,0.0148,0.4205,0.0047</t>
-  </si>
-  <si>
-    <t>0.8667,0.0174,0.0615,0.0260</t>
-  </si>
-  <si>
-    <t>0.4295,0.0432,0.6110,0.0164</t>
-  </si>
-  <si>
-    <t>0.8701,0.0140,0.0819,0.0265</t>
-  </si>
-  <si>
-    <t>0.8384,0.0049,0.2653,0.0023</t>
-  </si>
-  <si>
-    <t>0.6020,0.1886,0.0131,0.0334</t>
-  </si>
-  <si>
-    <t>0.9206,0.0126,0.0044,0.0239</t>
-  </si>
-  <si>
-    <t>0.1331,0.4506,0.6954,0.0451</t>
-  </si>
-  <si>
-    <t>0.7532,0.1531,0.0339,0.0137</t>
-  </si>
-  <si>
-    <t>0.8622,0.0418,0.0048,0.0151</t>
-  </si>
-  <si>
-    <t>0.5790,0.1476,0.1273,0.1345</t>
-  </si>
-  <si>
-    <t>0.3611,0.3962,0.0240,0.0272</t>
-  </si>
-  <si>
-    <t>0.8348,0.0701,0.0076,0.0128</t>
-  </si>
-  <si>
-    <t>0.5284,0.2786,0.1546,0.0360</t>
-  </si>
-  <si>
-    <t>0.8568,0.0052,0.1773,0.0053</t>
-  </si>
-  <si>
-    <t>0.5730,0.0162,0.4981,0.0049</t>
-  </si>
-  <si>
-    <t>0.9091,0.0145,0.0617,0.0063</t>
-  </si>
-  <si>
-    <t>0.3669,0.0841,0.6609,0.0057</t>
-  </si>
-  <si>
-    <t>0.6891,0.2821,0.0236,0.0100</t>
-  </si>
-  <si>
-    <t>0.8321,0.0064,0.1734,0.0159</t>
-  </si>
-  <si>
-    <t>0.8873,0.0182,0.0029,0.0253</t>
-  </si>
-  <si>
-    <t>0.5813,0.2110,0.0245,0.0355</t>
-  </si>
-  <si>
-    <t>0.7724,0.1140,0.0138,0.0197</t>
-  </si>
-  <si>
-    <t>0.6176,0.1896,0.0273,0.0326</t>
-  </si>
-  <si>
-    <t>0.1761,0.1843,0.8003,0.0221</t>
-  </si>
-  <si>
-    <t>0.2069,0.1283,0.8175,0.0020</t>
-  </si>
-  <si>
-    <t>0.8400,0.0162,0.1134,0.0207</t>
-  </si>
-  <si>
-    <t>0.5318,0.0176,0.6359,0.0047</t>
-  </si>
-  <si>
-    <t>0.0052,0.4281,0.9878,0.0003</t>
-  </si>
-  <si>
-    <t>0.2155,0.2462,0.7062,0.0033</t>
-  </si>
-  <si>
-    <t>0.8771,0.0256,0.0024,0.0144</t>
-  </si>
-  <si>
-    <t>0.7948,0.0477,0.0126,0.0483</t>
-  </si>
-  <si>
-    <t>0.7567,0.1325,0.0143,0.0160</t>
-  </si>
-  <si>
-    <t>0.2175,0.3277,0.6822,0.0322</t>
-  </si>
-  <si>
-    <t>0.7958,0.0477,0.0054,0.0234</t>
-  </si>
-  <si>
-    <t>0.7957,0.0347,0.0140,0.0776</t>
-  </si>
-  <si>
-    <t>0.9023,0.0521,0.0032,0.0048</t>
-  </si>
-  <si>
-    <t>0.0474,0.8633,0.5989,0.0060</t>
-  </si>
-  <si>
-    <t>0.7116,0.0095,0.3684,0.0086</t>
-  </si>
-  <si>
-    <t>0.6618,0.0234,0.4780,0.0044</t>
-  </si>
-  <si>
-    <t>0.0644,0.8383,0.5795,0.0101</t>
-  </si>
-  <si>
-    <t>0.2376,0.0076,0.8958,0.0013</t>
-  </si>
-  <si>
-    <t>0.3795,0.6114,0.0438,0.0084</t>
-  </si>
-  <si>
-    <t>0.2897,0.7018,0.0564,0.0090</t>
-  </si>
-  <si>
-    <t>0.8973,0.0104,0.0050,0.0443</t>
-  </si>
-  <si>
-    <t>0.7316,0.0897,0.1184,0.0741</t>
-  </si>
-  <si>
-    <t>0.2910,0.4484,0.4776,0.0134</t>
-  </si>
-  <si>
-    <t>0.2233,0.4343,0.5764,0.0095</t>
-  </si>
-  <si>
-    <t>0.5229,0.2237,0.2607,0.0045</t>
-  </si>
-  <si>
-    <t>0.1743,0.8232,0.1188,0.0029</t>
-  </si>
-  <si>
-    <t>0.0041,0.9233,0.9489,0.0011</t>
-  </si>
-  <si>
-    <t>0.8116,0.0565,0.0185,0.0416</t>
-  </si>
-  <si>
-    <t>0.7465,0.0227,0.0184,0.1808</t>
-  </si>
-  <si>
-    <t>0.9247,0.0118,0.0053,0.0272</t>
-  </si>
-  <si>
-    <t>0.6865,0.0532,0.0403,0.1747</t>
-  </si>
-  <si>
-    <t>0.7374,0.0572,0.0256,0.0862</t>
-  </si>
-  <si>
-    <t>0.9055,0.0089,0.0056,0.0516</t>
-  </si>
-  <si>
-    <t>0.0631,0.4189,0.8684,0.0076</t>
-  </si>
-  <si>
-    <t>0.2749,0.0656,0.7410,0.0089</t>
-  </si>
-  <si>
-    <t>0.6045,0.0654,0.3963,0.0071</t>
-  </si>
-  <si>
-    <t>0.0925,0.4745,0.7919,0.0077</t>
-  </si>
-  <si>
-    <t>0.0515,0.7324,0.7467,0.0049</t>
-  </si>
-  <si>
-    <t>0.7247,0.1483,0.1008,0.0107</t>
-  </si>
-  <si>
-    <t>0.6252,0.1760,0.0325,0.0458</t>
-  </si>
-  <si>
-    <t>0.5291,0.2405,0.0163,0.0313</t>
-  </si>
-  <si>
-    <t>0.7247,0.1154,0.0068,0.0158</t>
-  </si>
-  <si>
-    <t>0.8271,0.0205,0.0057,0.0574</t>
-  </si>
-  <si>
-    <t>0.9052,0.0548,0.0041,0.0060</t>
-  </si>
-  <si>
-    <t>0.7222,0.0469,0.0095,0.0684</t>
-  </si>
-  <si>
-    <t>0.8871,0.0207,0.0041,0.0243</t>
-  </si>
-  <si>
-    <t>0.6647,0.1055,0.0066,0.0314</t>
-  </si>
-  <si>
-    <t>0.7854,0.1080,0.0246,0.0263</t>
-  </si>
-  <si>
-    <t>0.8192,0.0310,0.0029,0.0316</t>
-  </si>
-  <si>
-    <t>0.7666,0.0209,0.0050,0.0939</t>
-  </si>
-  <si>
-    <t>0.8775,0.0397,0.0051,0.0147</t>
-  </si>
-  <si>
-    <t>0.8736,0.0351,0.0063,0.0199</t>
-  </si>
-  <si>
-    <t>0.7836,0.0513,0.0206,0.0548</t>
-  </si>
-  <si>
-    <t>0.6533,0.1335,0.0224,0.0460</t>
-  </si>
-  <si>
-    <t>0.8625,0.0291,0.0060,0.0319</t>
-  </si>
-  <si>
-    <t>0.0639,0.1037,0.9496,0.0030</t>
-  </si>
-  <si>
-    <t>0.8923,0.0147,0.0601,0.0104</t>
-  </si>
-  <si>
-    <t>0.9653,0.0070,0.0066,0.0045</t>
-  </si>
-  <si>
-    <t>0.8116,0.0333,0.1226,0.0177</t>
-  </si>
-  <si>
-    <t>0.5037,0.2688,0.0173,0.0255</t>
-  </si>
-  <si>
-    <t>0.5894,0.1450,0.0083,0.0349</t>
-  </si>
-  <si>
-    <t>0.4853,0.4038,0.0189,0.0131</t>
-  </si>
-  <si>
-    <t>0.4441,0.3400,0.0262,0.0298</t>
-  </si>
-  <si>
-    <t>0.7388,0.1568,0.0050,0.0088</t>
-  </si>
-  <si>
-    <t>0.1566,0.7330,0.0574,0.0355</t>
-  </si>
-  <si>
-    <t>0.7981,0.0973,0.0115,0.0167</t>
-  </si>
-  <si>
-    <t>0.9649,0.0081,0.0023,0.0055</t>
-  </si>
-  <si>
-    <t>0.9137,0.0094,0.0373,0.0315</t>
-  </si>
-  <si>
-    <t>0.7775,0.1044,0.0422,0.0258</t>
-  </si>
-  <si>
-    <t>0.8400,0.0257,0.0367,0.0689</t>
-  </si>
-  <si>
-    <t>0.4700,0.2854,0.0901,0.0941</t>
-  </si>
-  <si>
-    <t>0.3665,0.5239,0.0937,0.0222</t>
-  </si>
-  <si>
-    <t>0.4327,0.4141,0.0134,0.0152</t>
-  </si>
-  <si>
-    <t>0.4779,0.3880,0.0196,0.0130</t>
-  </si>
-  <si>
-    <t>0.0242,0.9429,0.5108,0.0116</t>
-  </si>
-  <si>
-    <t>0.7090,0.1206,0.0111,0.0262</t>
-  </si>
-  <si>
-    <t>0.7502,0.1434,0.0313,0.0272</t>
-  </si>
-  <si>
-    <t>0.6403,0.1726,0.0202,0.0262</t>
-  </si>
-  <si>
-    <t>0.6626,0.0689,0.0108,0.0673</t>
-  </si>
-  <si>
-    <t>0.6812,0.1603,0.0121,0.0218</t>
-  </si>
-  <si>
-    <t>0.6443,0.0589,0.0085,0.1000</t>
-  </si>
-  <si>
-    <t>0.6811,0.0737,0.0386,0.0944</t>
-  </si>
-  <si>
-    <t>0.8091,0.0574,0.0140,0.0321</t>
-  </si>
-  <si>
-    <t>0.8525,0.0545,0.0057,0.0145</t>
-  </si>
-  <si>
-    <t>0.7625,0.0557,0.0107,0.0452</t>
-  </si>
-  <si>
-    <t>0.6801,0.0841,0.0182,0.0734</t>
-  </si>
-  <si>
-    <t>0.5243,0.1571,0.3517,0.0198</t>
-  </si>
-  <si>
-    <t>0.7571,0.0280,0.3190,0.0034</t>
-  </si>
-  <si>
-    <t>0.3427,0.2169,0.5029,0.0032</t>
-  </si>
-  <si>
-    <t>0.9113,0.0050,0.0876,0.0052</t>
-  </si>
-  <si>
-    <t>0.8157,0.0711,0.0454,0.0295</t>
-  </si>
-  <si>
-    <t>0.9520,0.0085,0.0077,0.0102</t>
-  </si>
-  <si>
-    <t>0.9548,0.0062,0.0116,0.0076</t>
-  </si>
-  <si>
-    <t>0.8590,0.0474,0.0415,0.0255</t>
-  </si>
-  <si>
-    <t>0.8051,0.0094,0.0065,0.1502</t>
-  </si>
-  <si>
-    <t>0.7239,0.0084,0.0077,0.2714</t>
-  </si>
-  <si>
-    <t>0.9512,0.0076,0.0030,0.0185</t>
-  </si>
-  <si>
-    <t>0.7753,0.0201,0.0160,0.1572</t>
-  </si>
-  <si>
-    <t>0.0744,0.6449,0.7033,0.0330</t>
-  </si>
-  <si>
-    <t>0.8542,0.0413,0.0105,0.0302</t>
-  </si>
-  <si>
-    <t>0.6568,0.1864,0.0218,0.0254</t>
-  </si>
-  <si>
-    <t>0.9295,0.0058,0.0014,0.0249</t>
-  </si>
-  <si>
-    <t>0.8197,0.0558,0.0060,0.0212</t>
-  </si>
-  <si>
-    <t>0.8811,0.0305,0.0099,0.0231</t>
-  </si>
-  <si>
-    <t>0.9269,0.0067,0.0014,0.0214</t>
-  </si>
-  <si>
-    <t>0.6646,0.1800,0.0126,0.0190</t>
-  </si>
-  <si>
-    <t>0.0095,0.8946,0.8775,0.0077</t>
-  </si>
-  <si>
-    <t>0.9500,0.0082,0.0015,0.0118</t>
-  </si>
-  <si>
-    <t>0.8793,0.0136,0.0036,0.0424</t>
-  </si>
-  <si>
-    <t>0.7767,0.1145,0.0361,0.0209</t>
-  </si>
-  <si>
-    <t>0.7394,0.0882,0.0230,0.0445</t>
-  </si>
-  <si>
-    <t>0.8413,0.0879,0.0050,0.0079</t>
-  </si>
-  <si>
-    <t>0.7798,0.0941,0.0136,0.0235</t>
-  </si>
-  <si>
-    <t>0.6824,0.2248,0.0222,0.0167</t>
-  </si>
-  <si>
-    <t>0.8088,0.0943,0.0062,0.0097</t>
-  </si>
-  <si>
-    <t>0.8505,0.0217,0.0030,0.0316</t>
-  </si>
-  <si>
-    <t>0.7033,0.0598,0.0074,0.0588</t>
-  </si>
-  <si>
-    <t>0.8536,0.0317,0.0069,0.0252</t>
-  </si>
-  <si>
-    <t>0.5669,0.2654,0.0186,0.0238</t>
-  </si>
-  <si>
-    <t>0.9534,0.0090,0.0019,0.0081</t>
-  </si>
-  <si>
-    <t>0.7862,0.0334,0.0094,0.0651</t>
-  </si>
-  <si>
-    <t>0.7593,0.0700,0.0147,0.0403</t>
-  </si>
-  <si>
-    <t>0.6079,0.2105,0.0496,0.0415</t>
-  </si>
-  <si>
-    <t>0.4552,0.2613,0.0333,0.0560</t>
-  </si>
-  <si>
-    <t>0.4527,0.4671,0.0510,0.0141</t>
-  </si>
-  <si>
-    <t>0.1039,0.8531,0.1260,0.0270</t>
-  </si>
-  <si>
-    <t>0.7621,0.0998,0.0374,0.0457</t>
-  </si>
-  <si>
-    <t>0.7807,0.0817,0.0057,0.0163</t>
-  </si>
-  <si>
-    <t>0.6750,0.0596,0.0224,0.1214</t>
-  </si>
-  <si>
-    <t>0.8152,0.0570,0.0025,0.0122</t>
-  </si>
-  <si>
-    <t>0.6504,0.1303,0.0252,0.0516</t>
-  </si>
-  <si>
-    <t>0.1979,0.0767,0.8459,0.0057</t>
-  </si>
-  <si>
-    <t>0.9087,0.0349,0.0044,0.0091</t>
-  </si>
-  <si>
-    <t>0.5568,0.1364,0.3651,0.0296</t>
-  </si>
-  <si>
-    <t>0.7544,0.0136,0.3446,0.0033</t>
-  </si>
-  <si>
-    <t>0.6852,0.0256,0.4028,0.0074</t>
-  </si>
-  <si>
-    <t>0.3053,0.1104,0.7361,0.0069</t>
-  </si>
-  <si>
-    <t>0.5499,0.0294,0.5925,0.0068</t>
-  </si>
-  <si>
-    <t>0.2451,0.0160,0.8658,0.0026</t>
-  </si>
-  <si>
-    <t>0.5309,0.0347,0.5572,0.0066</t>
-  </si>
-  <si>
-    <t>0.8923,0.0181,0.0295,0.0287</t>
-  </si>
-  <si>
-    <t>0.5686,0.0902,0.4386,0.0289</t>
-  </si>
-  <si>
-    <t>0.6485,0.1930,0.1417,0.0319</t>
-  </si>
-  <si>
-    <t>0.8475,0.0201,0.0302,0.0723</t>
-  </si>
-  <si>
-    <t>0.7379,0.1227,0.0128,0.0212</t>
-  </si>
-  <si>
-    <t>0.9496,0.0117,0.0104,0.0055</t>
-  </si>
-  <si>
-    <t>0.9177,0.0118,0.0094,0.0260</t>
-  </si>
-  <si>
-    <t>0.7581,0.0134,0.1648,0.0567</t>
-  </si>
-  <si>
-    <t>0.2857,0.4332,0.0392,0.0562</t>
-  </si>
-  <si>
-    <t>0.7458,0.1394,0.0068,0.0122</t>
-  </si>
-  <si>
-    <t>0.5217,0.1307,0.0178,0.0902</t>
-  </si>
-  <si>
-    <t>0.8080,0.0572,0.0071,0.0253</t>
-  </si>
-  <si>
-    <t>0.6981,0.1156,0.0220,0.0472</t>
-  </si>
-  <si>
-    <t>0.8999,0.0301,0.0087,0.0133</t>
-  </si>
-  <si>
-    <t>0.9027,0.0165,0.0680,0.0082</t>
-  </si>
-  <si>
-    <t>0.9565,0.0065,0.0036,0.0103</t>
-  </si>
-  <si>
-    <t>0.8884,0.0363,0.0523,0.0093</t>
-  </si>
-  <si>
-    <t>0.9642,0.0084,0.0060,0.0039</t>
-  </si>
-  <si>
-    <t>0.8158,0.0933,0.0776,0.0263</t>
-  </si>
-  <si>
-    <t>0.8819,0.0088,0.1202,0.0041</t>
-  </si>
-  <si>
-    <t>0.7381,0.0199,0.2922,0.0047</t>
-  </si>
-  <si>
-    <t>0.6928,0.0187,0.3898,0.0107</t>
-  </si>
-  <si>
-    <t>0.2801,0.2793,0.6226,0.0069</t>
-  </si>
-  <si>
-    <t>0.8405,0.0313,0.0077,0.0409</t>
-  </si>
-  <si>
-    <t>0.6207,0.0509,0.0082,0.1211</t>
-  </si>
-  <si>
-    <t>0.6464,0.1341,0.0182,0.0365</t>
-  </si>
-  <si>
-    <t>0.8258,0.0374,0.0068,0.0316</t>
-  </si>
-  <si>
-    <t>0.8137,0.0738,0.0073,0.0159</t>
-  </si>
-  <si>
-    <t>0.8599,0.0916,0.0047,0.0062</t>
-  </si>
-  <si>
-    <t>0.6047,0.1464,0.0131,0.0404</t>
-  </si>
-  <si>
-    <t>0.8774,0.0206,0.0035,0.0268</t>
-  </si>
-  <si>
-    <t>0.8029,0.0658,0.1228,0.0249</t>
-  </si>
-  <si>
-    <t>0.7623,0.0705,0.0274,0.0537</t>
-  </si>
-  <si>
-    <t>0.9030,0.0243,0.0087,0.0201</t>
-  </si>
-  <si>
-    <t>0.3688,0.0293,0.7302,0.0060</t>
-  </si>
-  <si>
-    <t>0.1977,0.0903,0.8204,0.0122</t>
-  </si>
-  <si>
-    <t>0.9380,0.0163,0.0339,0.0027</t>
-  </si>
-  <si>
-    <t>0.0520,0.0806,0.9659,0.0013</t>
-  </si>
-  <si>
-    <t>0.6678,0.1421,0.1759,0.0455</t>
-  </si>
-  <si>
-    <t>0.2166,0.2190,0.7215,0.0026</t>
-  </si>
-  <si>
-    <t>0.8216,0.0127,0.1465,0.0229</t>
-  </si>
-  <si>
-    <t>0.4769,0.1720,0.1164,0.1888</t>
-  </si>
-  <si>
-    <t>0.9622,0.0049,0.0128,0.0038</t>
-  </si>
-  <si>
-    <t>0.7460,0.0705,0.1493,0.0349</t>
-  </si>
-  <si>
-    <t>0.9519,0.0086,0.0063,0.0084</t>
-  </si>
-  <si>
-    <t>0.7499,0.1020,0.0105,0.0194</t>
-  </si>
-  <si>
-    <t>0.8889,0.0430,0.0064,0.0137</t>
-  </si>
-  <si>
-    <t>0.8401,0.0286,0.0023,0.0216</t>
-  </si>
-  <si>
-    <t>0.7429,0.1140,0.0089,0.0166</t>
-  </si>
-  <si>
-    <t>0.8451,0.0338,0.0110,0.0496</t>
-  </si>
-  <si>
-    <t>0.6351,0.2632,0.0477,0.0225</t>
-  </si>
-  <si>
-    <t>0.7490,0.0816,0.0057,0.0200</t>
-  </si>
-  <si>
-    <t>0.7262,0.0675,0.0116,0.0444</t>
-  </si>
-  <si>
-    <t>0.4331,0.0610,0.6063,0.0127</t>
-  </si>
-  <si>
-    <t>0.0627,0.4660,0.8689,0.0077</t>
-  </si>
-  <si>
-    <t>0.5372,0.0154,0.6614,0.0030</t>
-  </si>
-  <si>
-    <t>0.9421,0.0089,0.0315,0.0074</t>
-  </si>
-  <si>
-    <t>0.8880,0.0062,0.1322,0.0039</t>
-  </si>
-  <si>
-    <t>0.8960,0.0371,0.0336,0.0137</t>
-  </si>
-  <si>
-    <t>0.7930,0.0320,0.1908,0.0108</t>
-  </si>
-  <si>
-    <t>0.7403,0.0191,0.3012,0.0134</t>
-  </si>
-  <si>
-    <t>0.8467,0.0313,0.0204,0.0370</t>
-  </si>
-  <si>
-    <t>0.7506,0.0539,0.0397,0.0863</t>
-  </si>
-  <si>
-    <t>0.9154,0.0076,0.0108,0.0395</t>
-  </si>
-  <si>
-    <t>0.6018,0.0704,0.0582,0.2346</t>
-  </si>
-  <si>
-    <t>0.8825,0.0056,0.0057,0.1135</t>
-  </si>
-  <si>
-    <t>0.7986,0.0178,0.0064,0.0756</t>
+    <t>0.9742,0.0012,0.0069,0.0089</t>
+  </si>
+  <si>
+    <t>0.0200,0.0002,0.0006,0.9938</t>
+  </si>
+  <si>
+    <t>0.8829,0.0004,0.0010,0.2170</t>
+  </si>
+  <si>
+    <t>0.0349,0.0016,0.0007,0.9889</t>
+  </si>
+  <si>
+    <t>0.9965,0.0006,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9961,0.0014,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9933,0.0010,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.5889,0.0141,0.5087,0.0059</t>
+  </si>
+  <si>
+    <t>0.0136,0.0102,0.9698,0.0061</t>
+  </si>
+  <si>
+    <t>0.3901,0.0009,0.8751,0.0001</t>
+  </si>
+  <si>
+    <t>0.0178,0.0013,0.9889,0.0007</t>
+  </si>
+  <si>
+    <t>0.8842,0.0205,0.1021,0.0048</t>
+  </si>
+  <si>
+    <t>0.0004,0.9985,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0041,0.9911,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.0017,0.9934,0.0005,0.0031</t>
+  </si>
+  <si>
+    <t>0.0033,0.9906,0.0022,0.0020</t>
+  </si>
+  <si>
+    <t>0.0003,0.9987,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.7729,0.0004,0.1673,0.0144</t>
+  </si>
+  <si>
+    <t>0.4513,0.0040,0.6078,0.0123</t>
+  </si>
+  <si>
+    <t>0.0030,0.0009,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.1125,0.0126,0.8793,0.0148</t>
+  </si>
+  <si>
+    <t>0.1050,0.0065,0.9402,0.0022</t>
+  </si>
+  <si>
+    <t>0.1082,0.0027,0.9256,0.0025</t>
+  </si>
+  <si>
+    <t>0.0271,0.0100,0.9427,0.0410</t>
+  </si>
+  <si>
+    <t>0.6396,0.4929,0.0045,0.0011</t>
+  </si>
+  <si>
+    <t>0.4261,0.0614,0.5954,0.0069</t>
+  </si>
+  <si>
+    <t>0.0006,0.0060,0.9964,0.0031</t>
+  </si>
+  <si>
+    <t>0.0423,0.9588,0.0071,0.0014</t>
+  </si>
+  <si>
+    <t>0.9798,0.0057,0.0046,0.0032</t>
+  </si>
+  <si>
+    <t>0.9019,0.0210,0.0812,0.0039</t>
+  </si>
+  <si>
+    <t>0.8804,0.1680,0.0035,0.0017</t>
+  </si>
+  <si>
+    <t>0.0036,0.9880,0.1538,0.0010</t>
+  </si>
+  <si>
+    <t>0.0485,0.4240,0.6268,0.0061</t>
+  </si>
+  <si>
+    <t>0.5608,0.0013,0.4234,0.0144</t>
+  </si>
+  <si>
+    <t>0.0019,0.0024,0.9933,0.0033</t>
+  </si>
+  <si>
+    <t>0.2788,0.0075,0.8217,0.0064</t>
+  </si>
+  <si>
+    <t>0.0118,0.0159,0.9852,0.0018</t>
+  </si>
+  <si>
+    <t>0.0040,0.9895,0.0050,0.0012</t>
+  </si>
+  <si>
+    <t>0.0061,0.0018,0.9901,0.0020</t>
+  </si>
+  <si>
+    <t>0.1026,0.2237,0.0105,0.7377</t>
+  </si>
+  <si>
+    <t>0.0046,0.9866,0.0129,0.0035</t>
+  </si>
+  <si>
+    <t>0.0100,0.9624,0.0717,0.0045</t>
+  </si>
+  <si>
+    <t>0.0005,0.9933,0.0357,0.0073</t>
+  </si>
+  <si>
+    <t>0.0036,0.0132,0.9897,0.0027</t>
+  </si>
+  <si>
+    <t>0.0032,0.7307,0.9553,0.0025</t>
+  </si>
+  <si>
+    <t>0.0046,0.0003,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.9983,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.0040,0.9852,0.0058</t>
+  </si>
+  <si>
+    <t>0.0108,0.0161,0.9756,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0057,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9920,0.0005,0.0099,0.0002</t>
+  </si>
+  <si>
+    <t>0.9508,0.0121,0.0108,0.0247</t>
+  </si>
+  <si>
+    <t>0.0103,0.0089,0.9906,0.0027</t>
+  </si>
+  <si>
+    <t>0.9970,0.0006,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9937,0.0014,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.9771,0.0113,0.0083,0.0016</t>
+  </si>
+  <si>
+    <t>0.0011,0.8714,0.9735,0.0010</t>
+  </si>
+  <si>
+    <t>0.0013,0.0092,0.9958,0.0012</t>
+  </si>
+  <si>
+    <t>0.0017,0.0008,0.9959,0.0015</t>
+  </si>
+  <si>
+    <t>0.0011,0.9452,0.9380,0.0014</t>
+  </si>
+  <si>
+    <t>0.0013,0.0031,0.9954,0.0014</t>
+  </si>
+  <si>
+    <t>0.0257,0.9734,0.0021,0.0005</t>
+  </si>
+  <si>
+    <t>0.0052,0.9939,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9852,0.0014,0.0182,0.0003</t>
+  </si>
+  <si>
+    <t>0.0570,0.0604,0.9263,0.0144</t>
+  </si>
+  <si>
+    <t>0.0012,0.0022,0.9972,0.0008</t>
+  </si>
+  <si>
+    <t>0.0011,0.9620,0.9227,0.0004</t>
+  </si>
+  <si>
+    <t>0.0046,0.6759,0.9137,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.9969,0.4923,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.9884,0.9694,0.0001</t>
+  </si>
+  <si>
+    <t>0.0098,0.0017,0.0089,0.9895</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.0011,0.9983</t>
+  </si>
+  <si>
+    <t>0.0012,0.0027,0.0003,0.9991</t>
+  </si>
+  <si>
+    <t>0.0096,0.0018,0.0012,0.9951</t>
+  </si>
+  <si>
+    <t>0.0319,0.0001,0.0005,0.9912</t>
+  </si>
+  <si>
+    <t>0.0041,0.0016,0.0011,0.9966</t>
+  </si>
+  <si>
+    <t>0.0012,0.9588,0.8495,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.5143,0.9854,0.0005</t>
+  </si>
+  <si>
+    <t>0.0057,0.5069,0.9383,0.0035</t>
+  </si>
+  <si>
+    <t>0.0020,0.6972,0.9524,0.0006</t>
+  </si>
+  <si>
+    <t>0.0008,0.9197,0.9507,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9858,0.3793,0.0002</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9945,0.0029,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9924,0.0047,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9825,0.0035,0.0008,0.0053</t>
+  </si>
+  <si>
+    <t>0.9911,0.0049,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9944,0.0014,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9887,0.0069,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9908,0.0043,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9976,0.0005,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9979,0.0005,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9983,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9933,0.0035,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9977,0.0004,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.0116,0.0013,0.9829,0.0082</t>
+  </si>
+  <si>
+    <t>0.0149,0.0055,0.9739,0.0049</t>
+  </si>
+  <si>
+    <t>0.9963,0.0003,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.0209,0.0007,0.9896,0.0002</t>
+  </si>
+  <si>
+    <t>0.0076,0.9903,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0030,0.9928,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.0252,0.9642,0.0118,0.0042</t>
+  </si>
+  <si>
+    <t>0.1805,0.8459,0.0064,0.0063</t>
+  </si>
+  <si>
+    <t>0.0234,0.9771,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.0047,0.9923,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.8854,0.1611,0.0035,0.0022</t>
+  </si>
+  <si>
+    <t>0.7678,0.1163,0.0731,0.0335</t>
+  </si>
+  <si>
+    <t>0.8884,0.0006,0.2057,0.0011</t>
+  </si>
+  <si>
+    <t>0.5555,0.0333,0.3717,0.0513</t>
+  </si>
+  <si>
+    <t>0.6224,0.0376,0.4136,0.0036</t>
+  </si>
+  <si>
+    <t>0.0306,0.0047,0.0167,0.9728</t>
+  </si>
+  <si>
+    <t>0.0023,0.9935,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.0087,0.9828,0.0245,0.0026</t>
+  </si>
+  <si>
+    <t>0.0002,0.9963,0.0007,0.0070</t>
+  </si>
+  <si>
+    <t>0.0023,0.9691,0.5998,0.0019</t>
+  </si>
+  <si>
+    <t>0.0042,0.9948,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.9204,0.0973,0.0035,0.0025</t>
+  </si>
+  <si>
+    <t>0.7661,0.3393,0.0115,0.0031</t>
+  </si>
+  <si>
+    <t>0.9929,0.0016,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.9927,0.0007,0.0041,0.0007</t>
+  </si>
+  <si>
+    <t>0.9872,0.0009,0.0036,0.0045</t>
+  </si>
+  <si>
+    <t>0.9969,0.0006,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9912,0.0012,0.0017,0.0023</t>
+  </si>
+  <si>
+    <t>0.9968,0.0003,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9940,0.0015,0.0007,0.0013</t>
+  </si>
+  <si>
+    <t>0.9913,0.0012,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.0075,0.0255,0.9906,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.2609,0.9554,0.0034</t>
+  </si>
+  <si>
+    <t>0.0253,0.0492,0.9604,0.0006</t>
+  </si>
+  <si>
+    <t>0.0267,0.0120,0.9605,0.0028</t>
+  </si>
+  <si>
+    <t>0.9885,0.0014,0.0060,0.0003</t>
+  </si>
+  <si>
+    <t>0.9527,0.0075,0.0303,0.0021</t>
+  </si>
+  <si>
+    <t>0.4730,0.0006,0.7005,0.0021</t>
+  </si>
+  <si>
+    <t>0.9707,0.0041,0.0169,0.0013</t>
+  </si>
+  <si>
+    <t>0.1167,0.0010,0.0013,0.9637</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.0009,0.9993</t>
+  </si>
+  <si>
+    <t>0.0040,0.0028,0.0150,0.9890</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.0019,0.9985</t>
+  </si>
+  <si>
+    <t>0.0010,0.9135,0.9241,0.0035</t>
+  </si>
+  <si>
+    <t>0.9961,0.0013,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0743,0.9202,0.0012,0.0078</t>
+  </si>
+  <si>
+    <t>0.9883,0.0031,0.0023,0.0025</t>
+  </si>
+  <si>
+    <t>0.7011,0.2869,0.0046,0.0112</t>
+  </si>
+  <si>
+    <t>0.9896,0.0003,0.0010,0.0067</t>
+  </si>
+  <si>
+    <t>0.9390,0.0154,0.0137,0.0235</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.0005,0.1967,0.9886,0.0079</t>
+  </si>
+  <si>
+    <t>0.9393,0.0001,0.0002,0.1310</t>
+  </si>
+  <si>
+    <t>0.9844,0.0011,0.0011,0.0090</t>
+  </si>
+  <si>
+    <t>0.8582,0.1688,0.0108,0.0053</t>
+  </si>
+  <si>
+    <t>0.9802,0.0057,0.0063,0.0014</t>
+  </si>
+  <si>
+    <t>0.9425,0.0041,0.0300,0.0138</t>
+  </si>
+  <si>
+    <t>0.1902,0.3926,0.1438,0.1772</t>
+  </si>
+  <si>
+    <t>0.8374,0.0671,0.0910,0.0061</t>
+  </si>
+  <si>
+    <t>0.8703,0.1241,0.0128,0.0047</t>
+  </si>
+  <si>
+    <t>0.9929,0.0004,0.0015,0.0030</t>
+  </si>
+  <si>
+    <t>0.9879,0.0010,0.0018,0.0066</t>
+  </si>
+  <si>
+    <t>0.9874,0.0016,0.0022,0.0053</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9922,0.0010,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.9941,0.0020,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9946,0.0007,0.0019,0.0009</t>
+  </si>
+  <si>
+    <t>0.9955,0.0009,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.8746,0.1096,0.0034,0.0058</t>
+  </si>
+  <si>
+    <t>0.8604,0.2042,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.8012,0.3127,0.0013,0.0008</t>
+  </si>
+  <si>
+    <t>0.7994,0.2192,0.0297,0.0079</t>
+  </si>
+  <si>
+    <t>0.9637,0.0458,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9909,0.0057,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9955,0.0008,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9776,0.0383,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.0155,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.8790,0.1501,0.0139,0.0039</t>
+  </si>
+  <si>
+    <t>0.0033,0.0016,0.9958,0.0007</t>
+  </si>
+  <si>
+    <t>0.0183,0.0060,0.9743,0.0042</t>
+  </si>
+  <si>
+    <t>0.0053,0.0034,0.9923,0.0005</t>
+  </si>
+  <si>
+    <t>0.0693,0.0092,0.9412,0.0022</t>
+  </si>
+  <si>
+    <t>0.0069,0.0012,0.9935,0.0008</t>
+  </si>
+  <si>
+    <t>0.0077,0.0003,0.9955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0006,0.9952,0.0030</t>
+  </si>
+  <si>
+    <t>0.7075,0.0055,0.4421,0.0028</t>
+  </si>
+  <si>
+    <t>0.2963,0.0029,0.8238,0.0030</t>
+  </si>
+  <si>
+    <t>0.1139,0.0343,0.8119,0.0169</t>
+  </si>
+  <si>
+    <t>0.1498,0.0584,0.7837,0.0049</t>
+  </si>
+  <si>
+    <t>0.1273,0.0578,0.8452,0.0033</t>
+  </si>
+  <si>
+    <t>0.6577,0.0092,0.4702,0.0017</t>
+  </si>
+  <si>
+    <t>0.6553,0.0223,0.2483,0.0792</t>
+  </si>
+  <si>
+    <t>0.2119,0.0163,0.7710,0.0344</t>
+  </si>
+  <si>
+    <t>0.0506,0.9619,0.0032,0.0014</t>
+  </si>
+  <si>
+    <t>0.0181,0.9822,0.0020,0.0007</t>
+  </si>
+  <si>
+    <t>0.6654,0.5423,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9821,0.0200,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9951,0.0047,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9441,0.0121,0.0399,0.0010</t>
+  </si>
+  <si>
+    <t>0.9955,0.0001,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.8362,0.0022,0.0664,0.0620</t>
+  </si>
+  <si>
+    <t>0.6155,0.0053,0.3101,0.0452</t>
+  </si>
+  <si>
+    <t>0.9584,0.0003,0.0471,0.0011</t>
+  </si>
+  <si>
+    <t>0.0049,0.0163,0.9721,0.0120</t>
+  </si>
+  <si>
+    <t>0.0019,0.0068,0.9891,0.0073</t>
+  </si>
+  <si>
+    <t>0.3456,0.0133,0.7770,0.0053</t>
+  </si>
+  <si>
+    <t>0.0278,0.0055,0.9512,0.0050</t>
+  </si>
+  <si>
+    <t>0.0114,0.0497,0.9698,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0005,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9840,0.0062,0.0043,0.0023</t>
+  </si>
+  <si>
+    <t>0.9935,0.0012,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9931,0.0043,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9872,0.0089,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9958,0.0008,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9936,0.0009,0.0006,0.0024</t>
+  </si>
+  <si>
+    <t>0.9957,0.0009,0.0003,0.0011</t>
+  </si>
+  <si>
+    <t>0.0099,0.2418,0.9650,0.0013</t>
+  </si>
+  <si>
+    <t>0.3001,0.2355,0.6532,0.0114</t>
+  </si>
+  <si>
+    <t>0.7926,0.0050,0.1342,0.0387</t>
+  </si>
+  <si>
+    <t>0.0020,0.0011,0.9958,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9865,0.0389</t>
+  </si>
+  <si>
+    <t>0.0127,0.0072,0.9819,0.0019</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9980,0.0005</t>
+  </si>
+  <si>
+    <t>0.0114,0.0067,0.9751,0.0035</t>
+  </si>
+  <si>
+    <t>0.0052,0.0044,0.9911,0.0028</t>
+  </si>
+  <si>
+    <t>0.0089,0.0102,0.9699,0.0110</t>
+  </si>
+  <si>
+    <t>0.0058,0.0066,0.9833,0.0048</t>
+  </si>
+  <si>
+    <t>0.8564,0.0097,0.2296,0.0025</t>
+  </si>
+  <si>
+    <t>0.8723,0.0022,0.2059,0.0022</t>
+  </si>
+  <si>
+    <t>0.9635,0.0009,0.0248,0.0070</t>
+  </si>
+  <si>
+    <t>0.9825,0.0147,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9972,0.0003,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9974,0.0008,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9889,0.0060,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9957,0.0016,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0020,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9913,0.0019,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9923,0.0017,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.0085,0.0215,0.9616,0.0108</t>
+  </si>
+  <si>
+    <t>0.0035,0.0059,0.9906,0.0017</t>
+  </si>
+  <si>
+    <t>0.0080,0.0242,0.9872,0.0044</t>
+  </si>
+  <si>
+    <t>0.2516,0.0042,0.8455,0.0015</t>
+  </si>
+  <si>
+    <t>0.0315,0.0015,0.9740,0.0015</t>
+  </si>
+  <si>
+    <t>0.3975,0.0046,0.5211,0.0361</t>
+  </si>
+  <si>
+    <t>0.0208,0.0104,0.9669,0.0070</t>
+  </si>
+  <si>
+    <t>0.1502,0.0060,0.7401,0.0518</t>
+  </si>
+  <si>
+    <t>0.9880,0.0003,0.0009,0.0095</t>
+  </si>
+  <si>
+    <t>0.0125,0.0093,0.0003,0.9923</t>
+  </si>
+  <si>
+    <t>0.0480,0.0004,0.0003,0.9888</t>
+  </si>
+  <si>
+    <t>0.0030,0.0001,0.0009,0.9980</t>
+  </si>
+  <si>
+    <t>0.0029,0.0002,0.0001,0.9990</t>
+  </si>
+  <si>
+    <t>0.9733,0.0030,0.0013,0.0132</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2121,7 +2121,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2373,7 +2373,7 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
         <v>294</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3451,7 +3451,7 @@
         <v>262</v>
       </c>
       <c r="C109" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D109" t="s">
         <v>371</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3479,7 +3479,7 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
         <v>373</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4711,7 +4711,7 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
         <v>461</v>
@@ -4725,7 +4725,7 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
         <v>462</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5383,7 +5383,7 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
         <v>509</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
